--- a/library/02_Genshin_Impact.xlsx
+++ b/library/02_Genshin_Impact.xlsx
@@ -7,123 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wuthering Waves" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Genshin Impact" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wuthering Waves'!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Genshin Impact'!$A$1:$E$129</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-  </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-  </fills>
-  <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-  </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
-</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -407,47 +297,4 @@
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
-</file>
-
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Имя персонажа</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Стихия</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Редкость</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:D1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>